--- a/kortdata/F_FS.xlsx
+++ b/kortdata/F_FS.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Sliter loss problemen innan de hinner sätta rötter.</t>
+          <t>Sliter loss problemen innan de hinner sätta rötter. Har rivit fler undertak än de flesta har sett, och hittar alltid det som någon försökt dölja. Ibland går lite mer än nödvändigt sönder på vägen.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Letar alltid efter sista procenten kvalitet, och hyresgästerna märker det.</t>
+          <t>Letar alltid efter den sista procenten kvalitet, och hyresgästerna märker det. Byter trasiga kakelplattor som ingen annan ser. Tycker att "bra nog" är ett skällsord.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -573,7 +573,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Vet alltid mer än han borde.</t>
+          <t>Vet alltid mer än hen borde och delar sällan med sig av hur. Läser årsredovisningar som andra läser deckare. Om du vill veta något om konkurrenten, fråga här först.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Hittar felen innan besiktningsmannen hinner fram.</t>
+          <t>Hittar felen innan besiktningsmannen hinner fram, med en ficklampa och en misstanke. Har aldrig köpt en fastighet utan att först ha krupit under den. Tar lite tid, men köper aldrig grisen i säcken.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -639,7 +639,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Säljer is till eskimåer, och fastigheter till rätt pris.</t>
+          <t>Kan sälja en källarlokal som penthouse och få köparen att tacka för möjligheten. Vet alltid vad marknaden är beredd att betala, och lite till. Köper du något, se till att det inte är av Mäklaren.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -672,7 +672,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Får hyresgästerna att släcka lampan efter sig.</t>
+          <t>Får hyresgästerna att släcka lampan efter sig och tycka att det var deras egen idé. Har en app för varje mätare och en graf för varje kvartal. Energiklasserna kryper sakta men säkert uppåt.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">

--- a/kortdata/F_FS.xlsx
+++ b/kortdata/F_FS.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>En gång per kvartal: titta på en dold bricka hos en motspelare</t>
+          <t>När en motspelare får en dold bricka får ni titta på den</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ignorera även den första energiminusbrickan på varje fastighet.</t>
+          <t>Vid köp: dra tre DD-kort och behåll det bästa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
